--- a/www/flightdata/xlsx/eoss-331.xlsx
+++ b/www/flightdata/xlsx/eoss-331.xlsx
@@ -4260,7 +4260,7 @@
         <v>33886.75</v>
       </c>
       <c r="I2">
-        <v>813</v>
+        <v>573</v>
       </c>
       <c r="J2" t="s">
         <v>43</v>
